--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Noto Sans JP"/>
@@ -47,6 +47,27 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="48"/>
+      <color theme="1"/>
+      <name val="メイリオ"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -58,12 +79,47 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -92,9 +148,29 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -109,16 +185,238 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18A303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369A3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A33E03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8E03A3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="C99C00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="C9211E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000EE"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551A8B"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <dimension ref="A2:D16"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="23.34"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="87.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="87.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="87.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="87.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="87.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageMargins left="0.39375" right="0.39375" top="0.265277777777778" bottom="0.265277777777778" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>

--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -8,7 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="NameTag" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="List" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -17,6 +18,23 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t xml:space="preserve">名前</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仮名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">項目A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">項目B</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -148,28 +166,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -299,98 +321,98 @@
   <dimension ref="A2:D16"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="23.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="23.34"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="87.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="87.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="2"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="87.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="2"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="87.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="87.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -423,4 +445,41 @@
     <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="C1:F1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_DFF768C8211EBB309D6401594D2EB7C6E0C96E0D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B15EF9D0-3C9F-4BD9-A63B-8FE3E6FE5819}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_DFF768C8211EBB309D6401594D2EB7C6E0C96E0D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38E00E9D-8FE5-497C-8B6D-E98D89790811}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,13 +165,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -307,7 +307,7 @@
     <col min="1" max="4" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="45.4" customHeight="1">
+    <row r="2" spans="1:4" ht="41.25" customHeight="1">
       <c r="A2" s="1">
         <f>List!E2</f>
         <v>0</v>
@@ -325,29 +325,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A3" s="4">
+    <row r="3" spans="1:4" ht="21" customHeight="1">
+      <c r="A3" s="3">
         <f>List!D2</f>
         <v>0</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5">
+      <c r="B3" s="3"/>
+      <c r="C3" s="4">
         <f>List!D3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="87.95" customHeight="1">
-      <c r="A4" s="3">
+    <row r="4" spans="1:4" ht="87" customHeight="1">
+      <c r="A4" s="5">
         <f>List!C2</f>
         <v>0</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5">
         <f>List!C3</f>
         <v>0</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:4" ht="12"/>
     <row r="6" spans="1:4" ht="12"/>

--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_DFF768C8211EBB309D6401594D2EB7C6E0C96E0D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38E00E9D-8FE5-497C-8B6D-E98D89790811}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="11_DFF768C8211EBB309D6401594D2EB7C6E0C96E0D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96F869EF-7C82-435A-86F4-5550827939F0}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,7 +90,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -151,13 +151,33 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -172,6 +192,12 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -308,44 +334,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="41.25" customHeight="1">
-      <c r="A2" s="1">
-        <f>List!E2</f>
-        <v>0</v>
-      </c>
-      <c r="B2" s="1">
-        <f>List!F2</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="1">
-        <f>List!E3</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <f>List!F3</f>
-        <v>0</v>
+      <c r="A2" s="1" t="str">
+        <f>IF(List!E2="", "", List!E2)</f>
+        <v/>
+      </c>
+      <c r="B2" s="7" t="str">
+        <f>IF(List!F2="", "", List!F2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="6" t="str">
+        <f>IF(List!E3="", "", List!E3)</f>
+        <v/>
+      </c>
+      <c r="D2" s="2" t="str">
+        <f>IF(List!F3="", "", List!F3)</f>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21" customHeight="1">
-      <c r="A3" s="3">
-        <f>List!D2</f>
-        <v>0</v>
+      <c r="A3" s="3" t="str">
+        <f>IF(List!D2="", "", List!D2)</f>
+        <v/>
       </c>
       <c r="B3" s="3"/>
-      <c r="C3" s="4">
-        <f>List!D3</f>
-        <v>0</v>
+      <c r="C3" s="4" t="str">
+        <f>IF(List!D3="", "", List!D3)</f>
+        <v/>
       </c>
       <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4" ht="87" customHeight="1">
-      <c r="A4" s="5">
-        <f>List!C2</f>
-        <v>0</v>
+      <c r="A4" s="5" t="str">
+        <f>IF(List!C2="", "", List!C2)</f>
+        <v/>
       </c>
       <c r="B4" s="5"/>
-      <c r="C4" s="5">
-        <f>List!C3</f>
-        <v>0</v>
+      <c r="C4" s="5" t="str">
+        <f>IF(List!C3="", "", List!C3)</f>
+        <v/>
       </c>
       <c r="D4" s="5"/>
     </row>
